--- a/Windpumpe_Kennlinien_final.xlsx
+++ b/Windpumpe_Kennlinien_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{26BD9A47-B0B9-426B-B7E3-FF401D7F6EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{915DC7C4-7753-4481-B4C3-FA0FE38E864A}"/>
+  <xr:revisionPtr revIDLastSave="649" documentId="13_ncr:1_{26BD9A47-B0B9-426B-B7E3-FF401D7F6EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB34F49D-F479-45E6-910D-EAE397FDD1DA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10660" windowHeight="4070" firstSheet="5" activeTab="7" xr2:uid="{D5F8A724-D9F7-4A04-989C-AB7680564365}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10660" windowHeight="4070" firstSheet="7" activeTab="8" xr2:uid="{D5F8A724-D9F7-4A04-989C-AB7680564365}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotokennlinie" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Rotokennlinie für Plakat" sheetId="8" r:id="rId6"/>
     <sheet name="Pumpenkennlinie für Plakat" sheetId="7" r:id="rId7"/>
     <sheet name="Übersetzung" sheetId="6" r:id="rId8"/>
+    <sheet name="Wirkungsgrad" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>Anstellwinkel</t>
   </si>
@@ -124,6 +125,54 @@
   </si>
   <si>
     <t>Nenner</t>
+  </si>
+  <si>
+    <t>Windgeschwindigkeit</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>Zeit</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Gefördertes Wasser</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Pumpenhöhe</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Pumpenleistung</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Dichte</t>
+  </si>
+  <si>
+    <t>kg/m³</t>
+  </si>
+  <si>
+    <t>Windleistung</t>
+  </si>
+  <si>
+    <t>Rotorradius</t>
+  </si>
+  <si>
+    <t>Wirkungsgrad</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -9916,7 +9965,128 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2DD51-CF9D-4D1B-A07B-5701B6F98E19}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1">
+        <v>6.1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <v>15.56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>0.185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <f>B3*B4*9.81/B2</f>
+        <v>2.4201887853470435E-2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6">
+        <v>1.204</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <f>B6/2*B1*B1*B1*PI()*B8*B8</f>
+        <v>19.843249307069883</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8">
+        <v>0.215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9">
+        <f>B5/B7*100</f>
+        <v>0.12196534689934893</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A76316D1B09904ABF9B6AC3DCE62340" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e24679dc0c589eaa0105ec0c277e4139">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="49b69e14-5500-4824-9263-8af50c6ab18e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52dc8d077da8146764382cb4c1c6d6e4" ns2:_="">
     <xsd:import namespace="49b69e14-5500-4824-9263-8af50c6ab18e"/>
@@ -10054,12 +10224,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10070,11 +10234,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87A58638-B614-4110-AA3D-2586D29AD345}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4828B3B-B51E-4AD8-849A-D258F2D683AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4828B3B-B51E-4AD8-849A-D258F2D683AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87A58638-B614-4110-AA3D-2586D29AD345}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Windpumpe_Kennlinien_final.xlsx
+++ b/Windpumpe_Kennlinien_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="649" documentId="13_ncr:1_{26BD9A47-B0B9-426B-B7E3-FF401D7F6EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB34F49D-F479-45E6-910D-EAE397FDD1DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92BB4385-C73D-425E-9BC3-32CFED1A6EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10660" windowHeight="4070" firstSheet="7" activeTab="8" xr2:uid="{D5F8A724-D9F7-4A04-989C-AB7680564365}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10660" windowHeight="4070" firstSheet="8" activeTab="8" xr2:uid="{D5F8A724-D9F7-4A04-989C-AB7680564365}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotokennlinie" sheetId="1" r:id="rId1"/>
@@ -10081,12 +10081,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A76316D1B09904ABF9B6AC3DCE62340" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e24679dc0c589eaa0105ec0c277e4139">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="49b69e14-5500-4824-9263-8af50c6ab18e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52dc8d077da8146764382cb4c1c6d6e4" ns2:_="">
     <xsd:import namespace="49b69e14-5500-4824-9263-8af50c6ab18e"/>
@@ -10224,6 +10218,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10234,11 +10234,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4828B3B-B51E-4AD8-849A-D258F2D683AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87A58638-B614-4110-AA3D-2586D29AD345}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87A58638-B614-4110-AA3D-2586D29AD345}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4828B3B-B51E-4AD8-849A-D258F2D683AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
